--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Deep Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Deep Test Plan Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t xml:space="preserve">Project ID Number:</t>
   </si>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">PR-002</t>
   </si>
   <si>
-    <t xml:space="preserve">PCB Temperature rise is less than 40°C above ambient</t>
+    <t xml:space="preserve">PCB Temperature rise is less than 40°C above ambient during loaded operation</t>
   </si>
   <si>
     <t xml:space="preserve">PR-003</t>
@@ -109,13 +109,31 @@
     <t xml:space="preserve">5.0V Regulator ripple &lt; 50mV</t>
   </si>
   <si>
-    <t xml:space="preserve">Initial PCB Assembly Testing</t>
+    <t xml:space="preserve">Safety and Regulatory Requirements</t>
   </si>
   <si>
     <t xml:space="preserve">Test Item</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse polarity protection test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermal protection for the DRV8825 IC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage isolation between motor power and logic circuits of the DRV8825 IC</t>
   </si>
   <si>
     <t xml:space="preserve">PCB Sub-System Testing and Verification</t>
@@ -1204,9 +1222,13 @@
       <c r="R37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14"/>
+      <c r="A38" s="14" t="s">
+        <v>32</v>
+      </c>
       <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
+      <c r="C38" s="14" t="s">
+        <v>33</v>
+      </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
@@ -1224,9 +1246,13 @@
       <c r="R38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14"/>
+      <c r="A39" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="C39" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14"/>
@@ -1244,9 +1270,13 @@
       <c r="R39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14"/>
+      <c r="A40" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
+      <c r="C40" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
@@ -2145,7 +2175,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Deep Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Deep Test Plan Log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t xml:space="preserve">Project ID Number:</t>
   </si>
@@ -91,10 +91,16 @@
     <t xml:space="preserve">Up to 2.5A motor current output is measured</t>
   </si>
   <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
     <t xml:space="preserve">PR-002</t>
   </si>
   <si>
     <t xml:space="preserve">PCB Temperature rise is less than 40°C above ambient during loaded operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
   </si>
   <si>
     <t xml:space="preserve">PR-003</t>
@@ -1029,7 +1035,9 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
-      <c r="J27" s="4"/>
+      <c r="J27" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -1041,11 +1049,11 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
@@ -1053,7 +1061,9 @@
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
-      <c r="J28" s="4"/>
+      <c r="J28" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -1065,11 +1075,11 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
@@ -1077,7 +1087,9 @@
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
-      <c r="J29" s="4"/>
+      <c r="J29" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -1089,11 +1101,11 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
@@ -1101,7 +1113,9 @@
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
-      <c r="J30" s="4"/>
+      <c r="J30" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -1121,7 +1135,7 @@
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
-      <c r="J31" s="4"/>
+      <c r="J31" s="14"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -1141,7 +1155,7 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
-      <c r="J32" s="4"/>
+      <c r="J32" s="14"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -1161,7 +1175,7 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
-      <c r="J33" s="4"/>
+      <c r="J33" s="14"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -1173,7 +1187,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -1195,11 +1209,11 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -1223,11 +1237,11 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
@@ -1235,7 +1249,9 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
-      <c r="J38" s="4"/>
+      <c r="J38" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -1247,11 +1263,11 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
@@ -1259,7 +1275,7 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
-      <c r="J39" s="4"/>
+      <c r="J39" s="14"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -1271,11 +1287,11 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
@@ -1283,7 +1299,7 @@
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
-      <c r="J40" s="4"/>
+      <c r="J40" s="14"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -1303,7 +1319,7 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
-      <c r="J41" s="4"/>
+      <c r="J41" s="14"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -1323,7 +1339,7 @@
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
-      <c r="J42" s="4"/>
+      <c r="J42" s="14"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -1343,7 +1359,7 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
-      <c r="J43" s="4"/>
+      <c r="J43" s="14"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -1363,7 +1379,7 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
-      <c r="J44" s="4"/>
+      <c r="J44" s="14"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -1383,7 +1399,7 @@
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
-      <c r="J45" s="4"/>
+      <c r="J45" s="14"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -1403,7 +1419,7 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
-      <c r="J46" s="4"/>
+      <c r="J46" s="14"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -1423,7 +1439,7 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
-      <c r="J47" s="4"/>
+      <c r="J47" s="14"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -1443,7 +1459,7 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
-      <c r="J48" s="4"/>
+      <c r="J48" s="14"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -1463,7 +1479,7 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
-      <c r="J49" s="4"/>
+      <c r="J49" s="14"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -1483,7 +1499,7 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
-      <c r="J50" s="4"/>
+      <c r="J50" s="14"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -1503,7 +1519,7 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
-      <c r="J51" s="4"/>
+      <c r="J51" s="14"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -1523,7 +1539,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
-      <c r="J52" s="4"/>
+      <c r="J52" s="14"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -1543,7 +1559,7 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
-      <c r="J53" s="4"/>
+      <c r="J53" s="14"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -1563,7 +1579,7 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
-      <c r="J54" s="4"/>
+      <c r="J54" s="14"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -1583,7 +1599,7 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="14"/>
-      <c r="J55" s="4"/>
+      <c r="J55" s="14"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -1603,7 +1619,7 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
-      <c r="J56" s="4"/>
+      <c r="J56" s="14"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -1623,7 +1639,7 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
-      <c r="J57" s="4"/>
+      <c r="J57" s="14"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -1643,7 +1659,7 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
-      <c r="J58" s="4"/>
+      <c r="J58" s="14"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -1663,7 +1679,7 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
-      <c r="J59" s="4"/>
+      <c r="J59" s="14"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -1683,7 +1699,7 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
-      <c r="J60" s="4"/>
+      <c r="J60" s="14"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -1703,7 +1719,7 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
-      <c r="J61" s="4"/>
+      <c r="J61" s="14"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -1723,7 +1739,7 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
-      <c r="J62" s="4"/>
+      <c r="J62" s="14"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -1743,7 +1759,7 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
-      <c r="J63" s="4"/>
+      <c r="J63" s="14"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -1763,7 +1779,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
-      <c r="J64" s="4"/>
+      <c r="J64" s="14"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -1783,7 +1799,7 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
-      <c r="J65" s="4"/>
+      <c r="J65" s="14"/>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -1803,7 +1819,7 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
-      <c r="J66" s="4"/>
+      <c r="J66" s="14"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -1823,7 +1839,7 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
-      <c r="J67" s="4"/>
+      <c r="J67" s="14"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -1843,7 +1859,7 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
-      <c r="J68" s="4"/>
+      <c r="J68" s="14"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -1863,7 +1879,7 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
-      <c r="J69" s="4"/>
+      <c r="J69" s="14"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -1883,7 +1899,7 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
-      <c r="J70" s="4"/>
+      <c r="J70" s="14"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
@@ -1903,7 +1919,7 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="14"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -1923,7 +1939,7 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
-      <c r="J72" s="4"/>
+      <c r="J72" s="14"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -1943,7 +1959,7 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
-      <c r="J73" s="4"/>
+      <c r="J73" s="14"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -1963,7 +1979,7 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="14"/>
-      <c r="J74" s="4"/>
+      <c r="J74" s="14"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -1983,7 +1999,7 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
-      <c r="J75" s="4"/>
+      <c r="J75" s="14"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -2003,7 +2019,7 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
-      <c r="J76" s="4"/>
+      <c r="J76" s="14"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
@@ -2023,7 +2039,7 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
-      <c r="J77" s="4"/>
+      <c r="J77" s="14"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
@@ -2043,7 +2059,7 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
-      <c r="J78" s="4"/>
+      <c r="J78" s="14"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -2063,7 +2079,7 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
-      <c r="J79" s="4"/>
+      <c r="J79" s="14"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -2083,7 +2099,7 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
-      <c r="J80" s="4"/>
+      <c r="J80" s="14"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -2103,7 +2119,7 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
-      <c r="J81" s="4"/>
+      <c r="J81" s="14"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -2123,7 +2139,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
-      <c r="J82" s="4"/>
+      <c r="J82" s="14"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -2143,7 +2159,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
-      <c r="J83" s="4"/>
+      <c r="J83" s="14"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -2163,7 +2179,7 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="14"/>
-      <c r="J84" s="4"/>
+      <c r="J84" s="14"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -2175,7 +2191,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -2197,11 +2213,11 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D88" s="10"/>
       <c r="E88" s="10"/>
@@ -2233,7 +2249,7 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="14"/>
-      <c r="J89" s="4"/>
+      <c r="J89" s="14"/>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -2253,7 +2269,7 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
-      <c r="J90" s="4"/>
+      <c r="J90" s="14"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -2273,7 +2289,7 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
-      <c r="J91" s="4"/>
+      <c r="J91" s="14"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -2293,7 +2309,7 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="14"/>
-      <c r="J92" s="4"/>
+      <c r="J92" s="14"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -2313,7 +2329,7 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="14"/>
-      <c r="J93" s="4"/>
+      <c r="J93" s="14"/>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -2333,7 +2349,7 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="14"/>
-      <c r="J94" s="4"/>
+      <c r="J94" s="14"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -2353,7 +2369,7 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
-      <c r="J95" s="4"/>
+      <c r="J95" s="14"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -2373,7 +2389,7 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
-      <c r="J96" s="4"/>
+      <c r="J96" s="14"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -2393,7 +2409,7 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="14"/>
-      <c r="J97" s="4"/>
+      <c r="J97" s="14"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -2413,7 +2429,7 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="14"/>
-      <c r="J98" s="4"/>
+      <c r="J98" s="14"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -2433,7 +2449,7 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="14"/>
-      <c r="J99" s="4"/>
+      <c r="J99" s="14"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
@@ -2453,7 +2469,7 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="14"/>
-      <c r="J100" s="4"/>
+      <c r="J100" s="14"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -2473,7 +2489,7 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
-      <c r="J101" s="4"/>
+      <c r="J101" s="14"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -2493,7 +2509,7 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="14"/>
-      <c r="J102" s="4"/>
+      <c r="J102" s="14"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -2513,7 +2529,7 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
-      <c r="J103" s="4"/>
+      <c r="J103" s="14"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
